--- a/artfynd/A 14342-2026 artfynd.xlsx
+++ b/artfynd/A 14342-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318229</v>
       </c>
       <c r="B2" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132318228</v>
       </c>
       <c r="B3" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14342-2026 artfynd.xlsx
+++ b/artfynd/A 14342-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318229</v>
       </c>
       <c r="B2" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132318228</v>
       </c>
       <c r="B3" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14342-2026 artfynd.xlsx
+++ b/artfynd/A 14342-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318229</v>
       </c>
       <c r="B2" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132318228</v>
       </c>
       <c r="B3" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14342-2026 artfynd.xlsx
+++ b/artfynd/A 14342-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132318229</v>
       </c>
       <c r="B2" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132318228</v>
       </c>
       <c r="B3" t="n">
-        <v>97981</v>
+        <v>97982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
